--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N42_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N42_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.97820032867627</v>
+        <v>6.333957553409894</v>
       </c>
       <c r="D2" t="n">
-        <v>38.56263007423199</v>
+        <v>6.266427387062699</v>
       </c>
       <c r="E2" t="n">
-        <v>9.193627735832971</v>
+        <v>1.493964507072858</v>
       </c>
       <c r="F2" t="n">
-        <v>7.611236615996225</v>
+        <v>1.236825950099387</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.77116397956995</v>
+        <v>2.237814146680116</v>
       </c>
       <c r="D3" t="n">
-        <v>13.95625206740538</v>
+        <v>2.267890960953374</v>
       </c>
       <c r="E3" t="n">
-        <v>9.193627735832971</v>
+        <v>1.493964507072858</v>
       </c>
       <c r="F3" t="n">
-        <v>7.611236615996225</v>
+        <v>1.236825950099387</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.83975208792253</v>
+        <v>3.711459714287411</v>
       </c>
       <c r="D4" t="n">
-        <v>23.24749442254346</v>
+        <v>3.777717843663313</v>
       </c>
       <c r="E4" t="n">
-        <v>9.193627735832971</v>
+        <v>1.493964507072858</v>
       </c>
       <c r="F4" t="n">
-        <v>7.611236615996225</v>
+        <v>1.236825950099387</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.3000257873104</v>
+        <v>6.22375419043794</v>
       </c>
       <c r="D5" t="n">
-        <v>25.00321586390641</v>
+        <v>4.063022577884792</v>
       </c>
       <c r="E5" t="n">
-        <v>9.193627735832971</v>
+        <v>1.493964507072858</v>
       </c>
       <c r="F5" t="n">
-        <v>7.611236615996225</v>
+        <v>1.236825950099387</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.65051125625934</v>
+        <v>4.980708079142143</v>
       </c>
       <c r="D6" t="n">
-        <v>30.64327588404461</v>
+        <v>4.97953233115725</v>
       </c>
       <c r="E6" t="n">
-        <v>9.193627735832971</v>
+        <v>1.493964507072858</v>
       </c>
       <c r="F6" t="n">
-        <v>7.611236615996225</v>
+        <v>1.236825950099387</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>16.68464698766403</v>
+        <v>2.711255135495406</v>
       </c>
       <c r="D7" t="n">
-        <v>16.0365888555661</v>
+        <v>2.605945689029491</v>
       </c>
       <c r="E7" t="n">
-        <v>9.193627735832971</v>
+        <v>1.493964507072858</v>
       </c>
       <c r="F7" t="n">
-        <v>7.611236615996225</v>
+        <v>1.236825950099387</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.47336351129967</v>
+        <v>2.839421570586197</v>
       </c>
       <c r="D8" t="n">
-        <v>17.74581191497946</v>
+        <v>2.883694436184162</v>
       </c>
       <c r="E8" t="n">
-        <v>9.193627735832971</v>
+        <v>1.493964507072858</v>
       </c>
       <c r="F8" t="n">
-        <v>7.611236615996225</v>
+        <v>1.236825950099387</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>29.98472489080092</v>
+        <v>4.87251779475515</v>
       </c>
       <c r="D9" t="n">
-        <v>21.63173056337878</v>
+        <v>3.515156216549053</v>
       </c>
       <c r="E9" t="n">
-        <v>9.193627735832971</v>
+        <v>1.493964507072858</v>
       </c>
       <c r="F9" t="n">
-        <v>7.611236615996225</v>
+        <v>1.236825950099387</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
